--- a/artfynd/S 2980-2024 artfynd.xlsx
+++ b/artfynd/S 2980-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1145,10 +1145,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>202976</v>
+        <v>137366175</v>
       </c>
       <c r="B6" t="n">
-        <v>102171</v>
+        <v>102471</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1174,24 +1174,23 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hyhult, Vrå, Sm</t>
+          <t>Väg 533, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>398011</v>
+        <v>397957</v>
       </c>
       <c r="R6" t="n">
-        <v>6284714</v>
+        <v>6284751</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1215,17 +1214,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2006-06-18</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2006-06-18</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Norra vägslänten</t>
+          <t>3 ex, västra sidan av vägen, i ytterslänten</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,35 +1233,35 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Krister Wahlström</t>
+          <t>Edvin Åhman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Krister Wahlström</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/202976</t>
+          <t>https://artportalen.se/Sighting/137366175</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>202977</v>
+        <v>202976</v>
       </c>
       <c r="B7" t="n">
         <v>102171</v>
@@ -1302,10 +1301,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>397984</v>
+        <v>398011</v>
       </c>
       <c r="R7" t="n">
-        <v>6284728</v>
+        <v>6284714</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1372,6 +1371,123 @@
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/202976</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>202977</v>
+      </c>
+      <c r="B8" t="n">
+        <v>102171</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>692</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Hårginst</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Genista pilosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hyhult, Vrå, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>397984</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6284728</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Vrå</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2006-06-18</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2006-06-18</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Norra vägslänten</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/202977</t>
         </is>
@@ -1385,6 +1501,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 2980-2024 artfynd.xlsx
+++ b/artfynd/S 2980-2024 artfynd.xlsx
@@ -1148,7 +1148,7 @@
         <v>137366175</v>
       </c>
       <c r="B6" t="n">
-        <v>102471</v>
+        <v>102474</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/S 2980-2024 artfynd.xlsx
+++ b/artfynd/S 2980-2024 artfynd.xlsx
@@ -1148,7 +1148,7 @@
         <v>137366175</v>
       </c>
       <c r="B6" t="n">
-        <v>102474</v>
+        <v>102480</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/S 2980-2024 artfynd.xlsx
+++ b/artfynd/S 2980-2024 artfynd.xlsx
@@ -1148,7 +1148,7 @@
         <v>137366175</v>
       </c>
       <c r="B6" t="n">
-        <v>102480</v>
+        <v>102492</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/S 2980-2024 artfynd.xlsx
+++ b/artfynd/S 2980-2024 artfynd.xlsx
@@ -1148,7 +1148,7 @@
         <v>137366175</v>
       </c>
       <c r="B6" t="n">
-        <v>102492</v>
+        <v>102493</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/S 2980-2024 artfynd.xlsx
+++ b/artfynd/S 2980-2024 artfynd.xlsx
@@ -1148,7 +1148,7 @@
         <v>137366175</v>
       </c>
       <c r="B6" t="n">
-        <v>102493</v>
+        <v>102496</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/S 2980-2024 artfynd.xlsx
+++ b/artfynd/S 2980-2024 artfynd.xlsx
@@ -1148,7 +1148,7 @@
         <v>137366175</v>
       </c>
       <c r="B6" t="n">
-        <v>102496</v>
+        <v>102500</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
